--- a/mapping/npc_accountcontactrelation.xlsx
+++ b/mapping/npc_accountcontactrelation.xlsx
@@ -559,6 +559,41 @@
       <c r="G4" t="n">
         <v>100</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AccountContactRelation</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>AccountId</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Account ID</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>The household Account's own Id (via HouseholdAccount_Load).</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IsIncludedInGroup/IsPrimaryMember/IsActive/ContactId are deliberately NOT mapped as rows here -- this doc's Source Object is Account only, but their real derivation is Contact-side (npo02__Household_Naming_Order__c) or per-row synthesis, not a 1:1 Account field. See sql/transformations/110_npc_accountcontactrelation_load.sql's own header comment and validators/AccountContactRelation.md for the real logic -- added 2026-07-18 after a second architect's live review found these fields missing from the actual migrated data.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
